--- a/case_study_results/validation_Baxter/Inter-annotator-reliability.xlsx
+++ b/case_study_results/validation_Baxter/Inter-annotator-reliability.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="consensus" sheetId="1" state="visible" r:id="rId3"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2035" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2035" uniqueCount="380">
   <si>
     <t xml:space="preserve">Path ID</t>
   </si>
@@ -1049,9 +1049,6 @@
     <t xml:space="preserve">FTP on later WBMs (D0002 4.2.5–4.2.6) is an open lead because D0002 does not say whether files can be moved.</t>
   </si>
   <si>
-    <t xml:space="preserve">In the reference documents there is source describes tokens being stolen or impersonated. D0006 only mentions an authentication token in the message header, with no weakness.</t>
-  </si>
-  <si>
     <t xml:space="preserve">WBM runs Digi Net+OS (D0004), not an OS with access tokens.This doesn't mean this path is impossible.</t>
   </si>
   <si>
@@ -1154,7 +1151,7 @@
     <t xml:space="preserve">Definition</t>
   </si>
   <si>
-    <t xml:space="preserve">Validation (Validation Paths sheet)</t>
+    <t xml:space="preserve">Annotators sheet </t>
   </si>
   <si>
     <t xml:space="preserve">Strong evidence that the weakness-technique-attack pattern combination was explicitly described for this device in at least one of the documents.</t>
@@ -7378,10 +7375,10 @@
         <v>22</v>
       </c>
       <c r="N15" s="50" t="s">
+        <v>68</v>
+      </c>
+      <c r="O15" s="50" t="s">
         <v>337</v>
-      </c>
-      <c r="O15" s="50" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7745,7 +7742,7 @@
         <v>92</v>
       </c>
       <c r="O23" s="47" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P23" s="17"/>
     </row>
@@ -7879,7 +7876,7 @@
         <v>99</v>
       </c>
       <c r="O26" s="44" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8194,7 +8191,7 @@
         <v>111</v>
       </c>
       <c r="O33" s="39" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8382,7 +8379,7 @@
         <v>124</v>
       </c>
       <c r="O37" s="39" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8427,7 +8424,7 @@
         <v>128</v>
       </c>
       <c r="O38" s="49" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8472,7 +8469,7 @@
         <v>132</v>
       </c>
       <c r="O39" s="47" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8828,7 +8825,7 @@
         <v>160</v>
       </c>
       <c r="O47" s="53" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9008,7 +9005,7 @@
         <v>174</v>
       </c>
       <c r="O51" s="39" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9098,90 +9095,90 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="54" t="s">
+        <v>346</v>
+      </c>
+      <c r="B1" s="54" t="s">
         <v>347</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="C1" s="54" t="s">
         <v>348</v>
-      </c>
-      <c r="C1" s="54" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="55" t="s">
+        <v>349</v>
+      </c>
+      <c r="B2" s="55" t="s">
         <v>350</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="C2" s="56" t="s">
         <v>351</v>
-      </c>
-      <c r="C2" s="56" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="55" t="s">
+        <v>352</v>
+      </c>
+      <c r="B3" s="55" t="s">
         <v>353</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="C3" s="56" t="s">
         <v>354</v>
-      </c>
-      <c r="C3" s="56" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
+        <v>355</v>
+      </c>
+      <c r="B4" s="57" t="s">
+        <v>353</v>
+      </c>
+      <c r="C4" s="58" t="s">
         <v>356</v>
-      </c>
-      <c r="B4" s="57" t="s">
-        <v>354</v>
-      </c>
-      <c r="C4" s="58" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="57" t="s">
+        <v>357</v>
+      </c>
+      <c r="B5" s="57" t="s">
         <v>358</v>
       </c>
-      <c r="B5" s="57" t="s">
+      <c r="C5" s="58" t="s">
         <v>359</v>
-      </c>
-      <c r="C5" s="58" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="57" t="s">
+        <v>360</v>
+      </c>
+      <c r="B6" s="57" t="s">
         <v>361</v>
       </c>
-      <c r="B6" s="57" t="s">
+      <c r="C6" s="58" t="s">
         <v>362</v>
-      </c>
-      <c r="C6" s="58" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="59" t="s">
+        <v>363</v>
+      </c>
+      <c r="B7" s="59" t="s">
         <v>364</v>
       </c>
-      <c r="B7" s="59" t="s">
+      <c r="C7" s="60" t="s">
         <v>365</v>
-      </c>
-      <c r="C7" s="60" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
+        <v>366</v>
+      </c>
+      <c r="B8" s="59" t="s">
         <v>367</v>
       </c>
-      <c r="B8" s="59" t="s">
+      <c r="C8" s="60" t="s">
         <v>368</v>
-      </c>
-      <c r="C8" s="60" t="s">
-        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -9220,15 +9217,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="61" t="s">
+        <v>369</v>
+      </c>
+      <c r="B1" s="61" t="s">
         <v>370</v>
-      </c>
-      <c r="B1" s="61" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="62" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B2" s="63"/>
     </row>
@@ -9237,7 +9234,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="65" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9245,7 +9242,7 @@
         <v>21</v>
       </c>
       <c r="B4" s="63" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9253,7 +9250,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="63" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9261,7 +9258,7 @@
         <v>210</v>
       </c>
       <c r="B6" s="63" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9269,7 +9266,7 @@
         <v>211</v>
       </c>
       <c r="B7" s="63" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9278,16 +9275,16 @@
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="62" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B9" s="63"/>
     </row>
     <row r="10" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="64" t="s">
+        <v>378</v>
+      </c>
+      <c r="B10" s="63" t="s">
         <v>379</v>
-      </c>
-      <c r="B10" s="63" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
